--- a/SSTSS_GenSim_Tool/odd_selection_nested_structure.xlsx
+++ b/SSTSS_GenSim_Tool/odd_selection_nested_structure.xlsx
@@ -894,10 +894,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
